--- a/medford_dopolnitelnoe_lor_oborudovanie.xlsx
+++ b/medford_dopolnitelnoe_lor_oborudovanie.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Дополнительное ЛОР оборудование для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS, Heine — всего 20 позиций.</t>
+          <t>Дополнительное ЛОР оборудование для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS, Heine.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_dopolnitelnoe_lor_oborudovanie.xlsx
+++ b/medford_dopolnitelnoe_lor_oborudovanie.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать дополнительное ЛОР оборудование для клиники?</t>
+          <t>Что относят к дополнительному ЛОР-оборудованию?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Производитель, Время работы, часов, Частота вспышки). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Это приборы, расширяющие возможности базового ЛОР-комбайна: смотровые и операционные микроскопы, стробоскопы, эхосинускопы, ультразвуковые аппараты для санации миндалин, небулайзеры, налобные осветители, а также системы риноманометрии, видеонистагмоскопии и стабилометрии. Состав зависит от того, диагностический это кабинет, физиотерапевтический или расширенный.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Зачем ЛОР-врачу смотровой микроскоп?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Микроскоп даёт увеличенное освещённое изображение барабанной перепонки и структур наружного и среднего уха, что нужно для точной диагностики и микроманипуляций. Смотровые модели ATMOS i View 21 и i View 31 и Chammed OMS-2350 применяют при осмотре уха, туалете слухового прохода и контроле после вмешательств.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Что делает ЛОР-стробоскоп?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены ATMOS, Heine. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Стробоскоп синхронизирует вспышки света с колебаниями голосовых складок и позволяет в замедленном виде оценить их подвижность и симметрию. Это ключевой инструмент фониатрии при диагностике нарушений голоса. ATMOS Strobo 21 LED работает в диапазоне частоты вспышки 70–1000 Гц и дополняет ларингоскопию.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Для чего нужны ультразвуковые ЛОР-аппараты?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Ультразвуковые аппараты применяют для санации миндалин и ультразвуковой терапии в ЛОР-практике. Комплекс ТОНЗИЛЛОР-3ММ сочетает озоно-ультразвуковое воздействие и рассчитан на продолжительный режим работы. Такие приборы используют в лечении хронического тонзиллита и других состояний по назначению врача.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Что измеряет риноманометр и эхосинускоп?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Риноманометр (Euroclinic RINOPOCKET ED 200) оценивает носовое дыхание, измеряя поток и давление воздуха в полости носа. Эхосинускоп (Oriola Sinuscan-201) с помощью ультразвука ориентировочно оценивает состояние околоносовых пазух без лучевой нагрузки. Оба прибора относятся к функциональной ЛОР-диагностике.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Какие инструменты нужны лору?</t>
+          <t>Как выбрать оборудование под кабинет?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Сначала определите профиль приёма — диагностика, физиотерапия, фониатрия или функциональные исследования — и добирайте приборы под него. Учитывайте совместимость оптики с видеосистемой, расходники и режимы обработки. Полезно свериться со стандартами оснащения ЛОР-кабинета и наличием регистрационных удостоверений на технику.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Каковы требования СанПиН к ЛОР-к кабинету?</t>
+          <t>Нужно ли регистрационное удостоверение на эту технику?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Медицинские приборы должны иметь действующее регистрационное удостоверение Росздравнадзора для применения в ЛПУ. Перед закупкой проверьте наличие РУ на конкретную модель и её нахождение в реестре. Это условие законной эксплуатации оборудования в медицинской организации.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Можно ли применять аппарат для массажа барабанной перепонки самостоятельно?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Аппараты для пневмомассажа барабанной перепонки — профессиональное медицинское оборудование. Процедура имеет противопоказания, например острый гнойный отит или перфорацию перепонки. Решение о применении и назначении принимает врач-оториноларинголог после осмотра, самостоятельное использование без консультации не рекомендуется.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>dopolnitelnoe_lor_oborudovanie</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Дополнительное ЛОР оборудование для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS, Heine.</t>
+          <t>Дополнительное ЛОР-оборудование — приборы, расширяющие диагностические и лечебные возможности рабочего места оториноларинголога сверх базового ЛОР-комбайна. В категории собраны смотровые микроскопы ATMOS i View 21 и i View 31, оториноларингологический микроскоп Chammed OMS-2350, стробоскоп ATMOS Strobo 21 LED (частота вспышки 70–1000 Гц), эхосинускоп Oriola Sinuscan-201, ультразвуковые аппараты Trima ИНТРА-ЛОР и ТОНЗИЛЛОР-3ММ, небулайзер Chammed XCN5 (размер частиц 5,0 мкм), налобный осветитель HEINE ML4 LED (ресурс 50 000 часов), а также системы риноманометрии, видеонистагмоскопии и стабилометрии Euroclinic. Оборудование покрывает диагностику, физиотерапию и функциональные исследования ЛОР-кабинета.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое дополнительное ЛОР оборудование</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4634,7 +4672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4960,12 +4998,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите профиль кабинета</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается дополнительное ЛОР оборудование: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Базовый диагностический приём, физиотерапия, фониатрия и функциональная диагностика требуют разного оснащения. От профиля зависит, что добавлять к ЛОР-комбайну: оптику, ультразвук, небулайзеры или системы вестибулярных и дыхательных исследований.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5005,12 +5043,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Подберите оптику для осмотра</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Для детального осмотра барабанной перепонки и микроманипуляций в ухе используют смотровые микроскопы ATMOS i View 21 и i View 31 или оториноларингологический микроскоп Chammed OMS-2350. Налобный осветитель HEINE ML4 LED с ресурсом 50 000 часов даёт направленный свет при рутинном осмотре.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5050,12 +5088,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Добавьте приборы для фониатрии</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Производитель, Время работы, часов, Частота вспышки. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Оценку подвижности голосовых складок выполняют стробоскопом: ATMOS Strobo 21 LED работает в диапазоне частоты вспышки 70–1000 Гц. Стробоскопия дополняет ларингоскопию при диагностике нарушений голоса и подходит фониатрическому приёму.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5095,12 +5133,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Выберите физиотерапию и санацию</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: ATMOS, Heine.</t>
+          <t>Ультразвуковые аппараты Trima ИНТРА-ЛОР и ТОНЗИЛЛОР-3ММ применяют для санации миндалин и ультразвуковой терапии. Небулайзер Chammed XCN5 с размером частиц около 5,0 мкм орошает миндалины, гортань и пазухи лекарственным аэрозолем. Подбирайте под лечебные протоколы кабинета.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5140,12 +5178,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Закройте функциональную диагностику</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Эхосинускоп Oriola Sinuscan-201 оценивает состояние околоносовых пазух, риноманометр Euroclinic RINOPOCKET ED 200 измеряет носовое дыхание. Видеонистагмоскопы Euroclinic ED600 и стабилометрическая платформа ED800 исследуют вестибулярную функцию и равновесие при головокружении.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5185,12 +5223,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте совместимость и обработку</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Оптику и эндоскопические модули сверяйте с имеющейся видеосистемой, а сменные части и наконечники ультразвуковых аппаратов — с протоколами обработки. Заранее уточните расходники и режимы дезинфекции, чтобы оборудование стыковалось с текущим оснащением кабинета.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5240,7 +5278,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Дополнительное ЛОР оборудование подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены ATMOS, Heine. При выборе обращают внимание на страна производства, производитель, время работы, частота вспышки, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Дополнительное оснащение ЛОР-кабинета собирают под реальные задачи приёма. Для микрохирургии уха и осмотра барабанной перепонки берут смотровой микроскоп ATMOS i View или Chammed OMS-2350, для фониатрии — стробоскоп ATMOS Strobo 21 LED, для санации миндалин — ультразвуковой ТОНЗИЛЛОР. Функциональную диагностику головокружения и носового дыхания закрывают риноманометр, видеонистагмоскоп и стабилометрическая платформа Euroclinic. Сначала определите профиль кабинета, затем добирайте приборы под него.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5524,13 +5562,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое дополнительное ЛОР оборудование</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Дополнительное ЛОР оборудование — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов ATMOS, Heine. Подберём вариант под задачи вашего отделения.</t>
+          <t>Дополнительное ЛОР-оборудование дополняет базовый ЛОР-комбайн диагностическими, лечебными и функциональными приборами: смотровыми и операционными микроскопами, стробоскопами, эхосинускопами, ультразвуковыми аппаратами для санации миндалин, небулайзерами, налобными осветителями, а также системами риноманометрии, видеонистагмоскопии и стабилометрии. В каталоге собрана техника ATMOS, Chammed, Euroclinic, Oriola, Trima и HEINE, покрывающая осмотр уха, фониатрию, физиотерапию и исследование вестибулярной и дыхательной функции. Состав подбирают под профиль кабинета — диагностический, физиотерапевтический или расширенный с функциональными исследованиями, ориентируясь на задачи приёма и совместимость с уже имеющимся оснащением.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5567,13 +5605,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое дополнительное ЛОР-оборудование</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Производитель, Время работы, часов, Частота вспышки), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Дополнительное ЛОР-оборудование — приборы и инструменты, расширяющие диагностические и лечебные возможности базового рабочего места оториноларинголога. Оно дополняет ЛОР-комбайн оптикой, ультразвуком, физиотерапией и системами функциональной диагностики, позволяя закрыть задачи от осмотра барабанной перепонки до исследования носового дыхания и вестибулярной функции.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5610,13 +5648,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Диагностическое оснащение кабинета</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>К диагностическому блоку относят ЛОР-микроскопы для осмотра барабанной перепонки и микроманипуляций, эндоскопическое оборудование для вывода изображения носа и гортани на экран, стробоскопы для оценки голосовых складок, эхосинускопы и риноманометры. В каталоге эту группу представляют ATMOS, Chammed, Oriola и Euroclinic.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5653,13 +5691,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Физиотерапия и лечебные приборы</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Лечебный блок включает ультразвуковые ЛОР-аппараты для санации миндалин (Trima ИНТРА-ЛОР, ТОНЗИЛЛОР-3ММ) и небулайзеры для мелкодисперсного орошения миндалин, гортани и пазух лекарственным аэрозолем (Chammed XCN5, размер частиц около 5,0 мкм). Приборы применяют по назначению врача в рамках лечебных протоколов кабинета.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5676,6 +5714,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Функциональная диагностика в ЛОР-кабинете</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Расширенный кабинет дополняют системами функциональной диагностики: риноманометрия оценивает носовое дыхание, видеонистагмоскопия и стабилометрия исследуют вестибулярную функцию и равновесие при головокружении. Линейка Euroclinic (RINOPOCKET ED 200, ED600 VNYS, ED800) закрывает эти задачи, а вестибулярный вибратор ED500 применяют в диагностических пробах.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>dopolnitelnoe_lor_oborudovanie</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
